--- a/data/trans_dic/P3A_R1-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R1-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,89; 32,24</t>
+          <t>24,05; 32,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,28; 40,67</t>
+          <t>31,58; 40,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,82; 44,53</t>
+          <t>34,99; 44,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,51; 43,63</t>
+          <t>34,1; 43,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,3; 33,71</t>
+          <t>23,38; 33,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,9; 35,76</t>
+          <t>25,41; 36,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,7; 37,84</t>
+          <t>27,86; 37,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,76; 37,6</t>
+          <t>29,72; 37,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,79; 31,58</t>
+          <t>25,0; 31,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,17; 37,59</t>
+          <t>29,98; 37,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,89; 40,3</t>
+          <t>33,35; 40,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,43; 39,11</t>
+          <t>33,69; 39,48</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,16; 33,2</t>
+          <t>22,92; 33,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,81; 41,35</t>
+          <t>31,46; 41,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,31; 53,27</t>
+          <t>42,6; 53,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,38; 39,85</t>
+          <t>30,35; 39,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,46; 27,6</t>
+          <t>18,87; 28,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,87; 28,75</t>
+          <t>18,99; 28,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,9; 38,15</t>
+          <t>27,99; 37,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,71; 32,3</t>
+          <t>24,81; 32,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,37; 28,55</t>
+          <t>22,11; 28,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,17; 34,28</t>
+          <t>27,32; 34,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,33; 43,86</t>
+          <t>36,28; 43,68</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,72; 34,89</t>
+          <t>28,74; 34,89</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,02; 28,57</t>
+          <t>20,85; 28,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,89; 35,32</t>
+          <t>27,73; 35,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,48; 41,97</t>
+          <t>33,79; 42,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 33,15</t>
+          <t>8,3; 33,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,84; 17,41</t>
+          <t>7,77; 18,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,09; 24,92</t>
+          <t>15,3; 25,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,09; 34,92</t>
+          <t>20,16; 34,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,42; 30,12</t>
+          <t>19,32; 30,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,01; 24,96</t>
+          <t>18,85; 25,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,18; 31,38</t>
+          <t>25,28; 31,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,62; 39,13</t>
+          <t>31,29; 38,93</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,54; 30,77</t>
+          <t>10,13; 30,72</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,09; 22,96</t>
+          <t>18,08; 22,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,14; 29,53</t>
+          <t>24,16; 29,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,33; 38,07</t>
+          <t>32,39; 38,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,7; 32,61</t>
+          <t>26,89; 33,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,67; 15,64</t>
+          <t>10,62; 16,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,12; 21,75</t>
+          <t>15,53; 21,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,91; 23,64</t>
+          <t>17,83; 23,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,09; 27,85</t>
+          <t>11,64; 28,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,04; 19,57</t>
+          <t>15,98; 19,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,73; 25,83</t>
+          <t>21,54; 25,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27,01; 31,17</t>
+          <t>26,92; 31,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,62; 29,42</t>
+          <t>17,91; 29,07</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,22; 21,43</t>
+          <t>13,23; 21,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,86; 27,68</t>
+          <t>20,13; 27,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,83; 26,59</t>
+          <t>19,71; 26,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,53; 27,89</t>
+          <t>19,26; 27,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,82; 10,25</t>
+          <t>5,87; 10,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,78; 13,44</t>
+          <t>8,72; 13,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,04; 16,07</t>
+          <t>11,09; 16,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,75; 20,34</t>
+          <t>13,07; 20,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,21; 13,5</t>
+          <t>9,2; 13,47</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,03; 17,98</t>
+          <t>13,98; 18,34</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,87; 19,97</t>
+          <t>15,68; 19,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,95; 21,98</t>
+          <t>15,82; 22,09</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,95</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,43</t>
+          <t>0,39; 3,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,75</t>
+          <t>0,74; 6,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,37</t>
+          <t>4,67; 7,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,38; 8,35</t>
+          <t>5,4; 8,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,99; 11,72</t>
+          <t>8,06; 11,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,19; 10,76</t>
+          <t>7,19; 10,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,26</t>
+          <t>3,91; 6,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,4; 6,77</t>
+          <t>4,42; 7,02</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,52; 9,41</t>
+          <t>6,67; 9,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,8; 9,09</t>
+          <t>5,79; 8,89</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,41; 22,31</t>
+          <t>19,32; 22,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,95; 29,29</t>
+          <t>25,92; 29,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30,94; 34,32</t>
+          <t>30,77; 34,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21,57; 29,77</t>
+          <t>20,28; 29,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,91; 13,1</t>
+          <t>10,95; 13,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,6; 16,02</t>
+          <t>13,64; 16,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,28; 19,85</t>
+          <t>17,34; 19,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,24; 21,95</t>
+          <t>16,71; 21,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,38; 17,32</t>
+          <t>15,48; 17,41</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,13; 22,19</t>
+          <t>20,09; 22,02</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24,4; 26,48</t>
+          <t>24,39; 26,42</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,63; 25,26</t>
+          <t>20,52; 25,42</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>112977; 152484</t>
+          <t>113729; 153706</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>136763; 177818</t>
+          <t>138077; 178243</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>149078; 190621</t>
+          <t>149817; 190496</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>174334; 220434</t>
+          <t>172272; 218041</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>71446; 103374</t>
+          <t>71697; 101894</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78313; 112449</t>
+          <t>79909; 114776</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96143; 131315</t>
+          <t>96705; 130061</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>132950; 167999</t>
+          <t>132801; 165592</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>193234; 246209</t>
+          <t>194923; 245663</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>226810; 282519</t>
+          <t>225332; 279371</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>254972; 312373</t>
+          <t>258530; 312566</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>318283; 372280</t>
+          <t>320749; 375796</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84983; 121830</t>
+          <t>84110; 121253</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>133217; 173185</t>
+          <t>131773; 174059</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>159622; 200957</t>
+          <t>160689; 202727</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>137232; 180030</t>
+          <t>137126; 179138</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68655; 102622</t>
+          <t>70162; 104620</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63782; 97189</t>
+          <t>64187; 97377</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>103871; 142028</t>
+          <t>104199; 140649</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>94527; 123570</t>
+          <t>94924; 125275</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>165280; 210938</t>
+          <t>163384; 211953</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>205632; 259467</t>
+          <t>206738; 259400</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>272311; 328702</t>
+          <t>271950; 327396</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>239604; 291136</t>
+          <t>239744; 291112</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>114004; 154967</t>
+          <t>113105; 154249</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>175520; 222286</t>
+          <t>174528; 223966</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>174123; 218303</t>
+          <t>175739; 219788</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46242; 221542</t>
+          <t>55474; 225243</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13152; 29219</t>
+          <t>13041; 30595</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39256; 64828</t>
+          <t>39805; 66160</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33382; 58005</t>
+          <t>33497; 57264</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32301; 50108</t>
+          <t>32145; 50461</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>135034; 177251</t>
+          <t>133902; 177679</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>223976; 279174</t>
+          <t>224836; 278432</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>217012; 268534</t>
+          <t>214707; 267125</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71253; 256824</t>
+          <t>84552; 256419</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>223955; 284315</t>
+          <t>223839; 282922</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>279800; 342223</t>
+          <t>279972; 340036</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>370289; 435993</t>
+          <t>370910; 439739</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>276309; 337506</t>
+          <t>278314; 343613</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>76046; 111487</t>
+          <t>75728; 114058</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>123226; 166291</t>
+          <t>118779; 166949</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>147199; 194268</t>
+          <t>146529; 191193</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>108485; 272370</t>
+          <t>113817; 274025</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>312933; 381898</t>
+          <t>311691; 381680</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>418108; 496916</t>
+          <t>414380; 496753</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>531338; 613221</t>
+          <t>529496; 611767</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>374711; 592169</t>
+          <t>360544; 585085</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>46357; 75117</t>
+          <t>46379; 74514</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>101183; 141026</t>
+          <t>102576; 140559</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>123078; 165027</t>
+          <t>122312; 165362</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92768; 132468</t>
+          <t>91473; 132151</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>33109; 58270</t>
+          <t>33363; 58556</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66829; 102362</t>
+          <t>66434; 101819</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81412; 118459</t>
+          <t>81786; 118861</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>107264; 171112</t>
+          <t>109932; 171361</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>84687; 124062</t>
+          <t>84584; 123863</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>178286; 228530</t>
+          <t>177698; 233141</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>215485; 271203</t>
+          <t>212960; 269670</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>209963; 289295</t>
+          <t>208287; 290845</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 9228</t>
+          <t>0; 8350</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5213</t>
+          <t>0; 4455</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1100; 9780</t>
+          <t>1107; 9506</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1904; 16229</t>
+          <t>1768; 14855</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>57101; 91797</t>
+          <t>58135; 91827</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59690; 92639</t>
+          <t>59862; 96290</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>86457; 126858</t>
+          <t>87194; 127663</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>54705; 81901</t>
+          <t>54763; 81837</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>60316; 96718</t>
+          <t>60418; 93464</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60576; 93203</t>
+          <t>60805; 96645</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>89149; 128700</t>
+          <t>91184; 131586</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>58072; 91116</t>
+          <t>58016; 89082</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>634433; 729533</t>
+          <t>631784; 726458</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>887559; 1002050</t>
+          <t>886801; 997382</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1044671; 1158825</t>
+          <t>1039015; 1155514</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>727956; 1004966</t>
+          <t>684551; 1008261</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>368193; 441834</t>
+          <t>369403; 446942</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>482615; 568257</t>
+          <t>483839; 573396</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>609324; 700156</t>
+          <t>611359; 698137</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>580689; 784895</t>
+          <t>597762; 786080</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1021891; 1150716</t>
+          <t>1028237; 1156246</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1402730; 1546430</t>
+          <t>1400115; 1534715</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1684260; 1828041</t>
+          <t>1683999; 1823602</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1364778; 1756426</t>
+          <t>1426381; 1767307</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R1-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R1-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,03%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,05; 32,5</t>
+          <t>23,57; 32,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,58; 40,77</t>
+          <t>30,93; 40,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34,99; 44,5</t>
+          <t>35,42; 44,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34,1; 43,16</t>
+          <t>34,6; 43,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,38; 33,22</t>
+          <t>23,02; 33,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,41; 36,5</t>
+          <t>25,33; 35,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,86; 37,48</t>
+          <t>27,59; 37,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,72; 37,06</t>
+          <t>29,3; 36,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>25,0; 31,51</t>
+          <t>24,66; 31,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,98; 37,17</t>
+          <t>30,56; 37,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33,35; 40,32</t>
+          <t>33,2; 39,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,69; 39,48</t>
+          <t>33,1; 38,73</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,92; 33,04</t>
+          <t>23,03; 32,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>31,46; 41,56</t>
+          <t>31,5; 41,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,6; 53,74</t>
+          <t>42,24; 53,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30,35; 39,65</t>
+          <t>30,58; 39,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,87; 28,13</t>
+          <t>18,66; 27,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,99; 28,81</t>
+          <t>19,02; 28,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,99; 37,78</t>
+          <t>27,95; 37,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,81; 32,74</t>
+          <t>23,68; 31,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,11; 28,69</t>
+          <t>22,27; 28,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,32; 34,28</t>
+          <t>27,33; 34,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,28; 43,68</t>
+          <t>36,61; 44,08</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>28,74; 34,89</t>
+          <t>28,34; 34,33</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,85; 28,44</t>
+          <t>21,3; 28,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,73; 35,58</t>
+          <t>27,6; 35,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,79; 42,26</t>
+          <t>33,54; 42,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,3; 33,71</t>
+          <t>27,34; 36,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,77; 18,23</t>
+          <t>7,91; 17,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,3; 25,43</t>
+          <t>15,5; 25,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,16; 34,47</t>
+          <t>20,77; 35,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,32; 30,34</t>
+          <t>19,68; 30,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18,85; 25,02</t>
+          <t>18,84; 25,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,28; 31,3</t>
+          <t>25,18; 31,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,29; 38,93</t>
+          <t>31,72; 39,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,13; 30,72</t>
+          <t>26,07; 33,36</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,08; 22,85</t>
+          <t>18,11; 22,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,16; 29,34</t>
+          <t>24,07; 29,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,39; 38,4</t>
+          <t>32,03; 37,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,89; 33,21</t>
+          <t>27,28; 32,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,62; 16,0</t>
+          <t>10,57; 15,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,53; 21,83</t>
+          <t>15,6; 21,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,83; 23,26</t>
+          <t>17,82; 23,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,64; 28,02</t>
+          <t>23,78; 29,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,98; 19,56</t>
+          <t>16,14; 19,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,54; 25,82</t>
+          <t>21,39; 25,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,92; 31,1</t>
+          <t>26,87; 31,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,91; 29,07</t>
+          <t>26,48; 30,47</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>13,23; 21,26</t>
+          <t>13,29; 21,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,13; 27,59</t>
+          <t>19,87; 27,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,71; 26,64</t>
+          <t>19,72; 26,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,26; 27,82</t>
+          <t>18,24; 25,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 10,3</t>
+          <t>5,7; 10,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,72; 13,37</t>
+          <t>8,68; 13,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,09; 16,12</t>
+          <t>11,18; 15,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,07; 20,37</t>
+          <t>16,9; 21,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,2; 13,47</t>
+          <t>9,35; 13,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,98; 18,34</t>
+          <t>14,07; 18,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,68; 19,86</t>
+          <t>15,63; 20,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,82; 22,09</t>
+          <t>18,11; 22,0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,33</t>
+          <t>0,39; 3,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,18</t>
+          <t>0,83; 7,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,37</t>
+          <t>4,74; 7,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,4; 8,68</t>
+          <t>5,39; 8,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,06; 11,8</t>
+          <t>7,96; 11,67</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,19; 10,75</t>
+          <t>6,91; 10,27</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,91; 6,05</t>
+          <t>3,8; 6,0</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4,42; 7,02</t>
+          <t>4,34; 6,85</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,67; 9,62</t>
+          <t>6,66; 9,66</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,79; 8,89</t>
+          <t>5,99; 8,75</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,32; 22,22</t>
+          <t>19,49; 22,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>25,92; 29,16</t>
+          <t>26,02; 29,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30,77; 34,22</t>
+          <t>30,91; 34,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20,28; 29,87</t>
+          <t>27,44; 30,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,95; 13,25</t>
+          <t>10,9; 13,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,64; 16,16</t>
+          <t>13,67; 16,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,34; 19,8</t>
+          <t>17,21; 19,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,71; 21,98</t>
+          <t>20,21; 22,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,48; 17,41</t>
+          <t>15,41; 17,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20,09; 22,02</t>
+          <t>20,0; 22,12</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24,39; 26,42</t>
+          <t>24,27; 26,41</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,52; 25,42</t>
+          <t>24,12; 26,1</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>196011</t>
+          <t>214305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>149616</t>
+          <t>159780</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>345627</t>
+          <t>374085</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>113729; 153706</t>
+          <t>111442; 152331</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>138077; 178243</t>
+          <t>135239; 178516</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>149817; 190496</t>
+          <t>151656; 192547</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>172272; 218041</t>
+          <t>190510; 238809</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>71697; 101894</t>
+          <t>70596; 102312</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79909; 114776</t>
+          <t>79654; 111855</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96705; 130061</t>
+          <t>95742; 130390</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>132801; 165592</t>
+          <t>142899; 177913</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>194923; 245663</t>
+          <t>192222; 246233</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>225332; 279371</t>
+          <t>229727; 279704</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>258530; 312566</t>
+          <t>257339; 309471</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>320749; 375796</t>
+          <t>343735; 402135</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>156479</t>
+          <t>168753</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>108996</t>
+          <t>116205</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>265475</t>
+          <t>284957</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84110; 121253</t>
+          <t>84491; 120305</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>131773; 174059</t>
+          <t>131901; 175060</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>160689; 202727</t>
+          <t>159354; 200292</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>137126; 179138</t>
+          <t>147625; 192495</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70162; 104620</t>
+          <t>69390; 102438</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64187; 97377</t>
+          <t>64285; 97584</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>104199; 140649</t>
+          <t>104051; 139833</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>94924; 125275</t>
+          <t>100210; 133268</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>163384; 211953</t>
+          <t>164522; 212499</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>206738; 259400</t>
+          <t>206860; 259442</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>271950; 327396</t>
+          <t>274359; 330406</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>239744; 291112</t>
+          <t>256747; 310941</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135209</t>
+          <t>149188</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40361</t>
+          <t>44766</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>175571</t>
+          <t>193953</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>113105; 154249</t>
+          <t>115521; 155100</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>174528; 223966</t>
+          <t>173691; 222038</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>175739; 219788</t>
+          <t>174416; 218750</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>55474; 225243</t>
+          <t>128935; 170519</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13041; 30595</t>
+          <t>13272; 29959</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39805; 66160</t>
+          <t>40321; 66659</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33497; 57264</t>
+          <t>34505; 58157</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32145; 50461</t>
+          <t>36779; 56841</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>133902; 177679</t>
+          <t>133793; 178584</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>224836; 278432</t>
+          <t>223989; 277838</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>214707; 267125</t>
+          <t>217699; 269271</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84552; 256419</t>
+          <t>171651; 219704</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>307276</t>
+          <t>337824</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>208737</t>
+          <t>228518</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>516013</t>
+          <t>566343</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>223839; 282922</t>
+          <t>224205; 282613</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>279972; 340036</t>
+          <t>278980; 342661</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>370910; 439739</t>
+          <t>366827; 434282</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>278314; 343613</t>
+          <t>308800; 371443</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>75728; 114058</t>
+          <t>75365; 113783</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>118779; 166949</t>
+          <t>119308; 164481</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>146529; 191193</t>
+          <t>146487; 194609</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>113817; 274025</t>
+          <t>204804; 251093</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>311691; 381680</t>
+          <t>314933; 381115</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>414380; 496753</t>
+          <t>411526; 492384</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>529496; 611767</t>
+          <t>528521; 612025</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>360544; 585085</t>
+          <t>527828; 607237</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111214</t>
+          <t>124221</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>145260</t>
+          <t>157351</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>256473</t>
+          <t>281572</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>46379; 74514</t>
+          <t>46577; 75131</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>102576; 140559</t>
+          <t>101250; 139555</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>122312; 165362</t>
+          <t>122408; 165331</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>91473; 132151</t>
+          <t>103587; 147607</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>33363; 58556</t>
+          <t>32437; 58127</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>66434; 101819</t>
+          <t>66118; 102637</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>81786; 118861</t>
+          <t>82430; 117367</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>109932; 171361</t>
+          <t>140435; 179049</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>84584; 123863</t>
+          <t>85979; 125115</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>177698; 233141</t>
+          <t>178821; 231030</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>212960; 269670</t>
+          <t>212206; 271618</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>208287; 290845</t>
+          <t>253318; 307772</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>66363</t>
+          <t>71343</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>72545</t>
+          <t>78256</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 8350</t>
+          <t>0; 9397</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4455</t>
+          <t>0; 5083</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1107; 9506</t>
+          <t>1121; 10216</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1768; 14855</t>
+          <t>1974; 16914</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>58135; 91827</t>
+          <t>59093; 90491</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>59862; 96290</t>
+          <t>59779; 93735</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>87194; 127663</t>
+          <t>86079; 126247</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>54763; 81837</t>
+          <t>58353; 86744</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>60418; 93464</t>
+          <t>58643; 92651</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60805; 96645</t>
+          <t>59782; 94319</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>91184; 131586</t>
+          <t>91103; 132039</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>58016; 89082</t>
+          <t>64738; 94579</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>912372</t>
+          <t>1001204</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>719332</t>
+          <t>777963</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1631703</t>
+          <t>1779167</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>631784; 726458</t>
+          <t>637233; 733028</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>886801; 997382</t>
+          <t>890153; 992195</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1039015; 1155514</t>
+          <t>1043844; 1153815</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>684551; 1008261</t>
+          <t>944475; 1058295</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>369403; 446942</t>
+          <t>367690; 441936</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>483839; 573396</t>
+          <t>484973; 575140</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>611359; 698137</t>
+          <t>606821; 702243</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>597762; 786080</t>
+          <t>734299; 817691</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1028237; 1156246</t>
+          <t>1023573; 1147206</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1400115; 1534715</t>
+          <t>1394112; 1541280</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1683999; 1823602</t>
+          <t>1675571; 1822906</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1426381; 1767307</t>
+          <t>1706869; 1847004</t>
         </is>
       </c>
     </row>
